--- a/data/Mapeamento de produtos e ações realizados pelo Detran-SP para o Painel Pnatrans.xlsx
+++ b/data/Mapeamento de produtos e ações realizados pelo Detran-SP para o Painel Pnatrans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\pabsantos\Projects\pnatrans_fichas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\pabsantos\Projects\pnatrans_fichas\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ADDF3B4-4EAA-4273-9BF2-55B978E3E906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E3A5B4F-FF3D-4BAE-99DF-6D76AD1E6F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="215">
   <si>
     <t>Id</t>
   </si>
@@ -83,6 +83,9 @@
     <t>Valor resultado</t>
   </si>
   <si>
+    <t>Observações</t>
+  </si>
+  <si>
     <t>Área responsável</t>
   </si>
   <si>
@@ -113,6 +116,9 @@
     <t>Valor resultado1</t>
   </si>
   <si>
+    <t>Observações1</t>
+  </si>
+  <si>
     <t>Área responsável1</t>
   </si>
   <si>
@@ -143,6 +149,9 @@
     <t>Valor resultado2</t>
   </si>
   <si>
+    <t>Observações2</t>
+  </si>
+  <si>
     <t>Área responsável2</t>
   </si>
   <si>
@@ -173,6 +182,9 @@
     <t>Ano referência3</t>
   </si>
   <si>
+    <t>Observações3</t>
+  </si>
+  <si>
     <t>Valor resultado3</t>
   </si>
   <si>
@@ -203,6 +215,9 @@
     <t>Ano referência4</t>
   </si>
   <si>
+    <t>Observações4</t>
+  </si>
+  <si>
     <t>Valor resultado4</t>
   </si>
   <si>
@@ -231,6 +246,9 @@
   </si>
   <si>
     <t>Ano referência5</t>
+  </si>
+  <si>
+    <t>Observações5</t>
   </si>
   <si>
     <t>Valor resultado5</t>
@@ -469,15 +487,282 @@
   <si>
     <t>https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Arquivos%20comprovat%C3%B3rios%202/2.Evid%C3%AAncia_Apresenta%C3%A7%C3%A3o_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Arquivos%20comprovat%C3%B3rios%202/2.Evid%C3%AAncia_Formul%C3%A1rio_Beatriz%20de%20Jesus%20Gon.pdf</t>
   </si>
+  <si>
+    <t>Diretoria de Administração e Logística (DAL)</t>
+  </si>
+  <si>
+    <t>Pilar 3 - Segurança Veicular</t>
+  </si>
+  <si>
+    <t>A3001</t>
+  </si>
+  <si>
+    <t>P3002</t>
+  </si>
+  <si>
+    <t>Minuta do Plano de Segurança Viária do Estado de São Paulo</t>
+  </si>
+  <si>
+    <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit, sed do eiusmod tempor incididunt ut labore et dolore magna aliqua. Ut enim ad minim veniam, quis nostrud exercitation ullamco laboris nisi ut aliquip ex ea commodo consequat. Duis aute irure dolor in reprehenderit in voluptate velit esse cillum dolore eu fugiat nulla pariatur. Excepteur sint occaecat cupidatat non proident, sunt in culpa qui officia deserunt mollit anim id est laborum.</t>
+  </si>
+  <si>
+    <t>Texto publicado</t>
+  </si>
+  <si>
+    <t>Produto atualizado</t>
+  </si>
+  <si>
+    <t>Divisão de Redução de Mortes e Lesões no Trânsito</t>
+  </si>
+  <si>
+    <t>https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Arquivos%20comprovat%C3%B3rios%201/EDUCA%C3%87%C3%83O%20NO%20TR%C3%82NSITO_Beatriz%20de%20Jesus%20Gon.pdf</t>
+  </si>
+  <si>
+    <t>felipe.lucena@detran.sp.gov.br</t>
+  </si>
+  <si>
+    <t>Felipe Gonçalves Lima de Lucena</t>
+  </si>
+  <si>
+    <t>Diretoria de Veículos Automotores (DVA)</t>
+  </si>
+  <si>
+    <t>NOVA AÇÃO</t>
+  </si>
+  <si>
+    <t>Sanitização de Bloqueios Administrativos</t>
+  </si>
+  <si>
+    <t>Saneamento massivo de bloqueios administrativos com padronização de fluxo de desbloqueio e regularização de registros veiculares. A iniciativa melhora a confiabilidade cadastral e reduz inconsistências no registro de veículos.</t>
+  </si>
+  <si>
+    <t>Quantidade de bloqueios sanitizados; pedidos de desbloqueio analisados</t>
+  </si>
+  <si>
+    <t>Diretoria de Veículos Automotores</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/37783c04-f32e-4913-ae3f-d34ce6be6230/ReportSectioneab0dd9520145024900a?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi</t>
+  </si>
+  <si>
+    <t>Monitoramento de Fraudes em Registros Veiculares</t>
+  </si>
+  <si>
+    <t>Implementação de painéis e mecanismos de monitoramento de irregularidades em registros veiculares e emissões de ATPV/ATPV-e, permitindo identificação de padrões suspeitos e encaminhamento de casos para apuração administrativa.</t>
+  </si>
+  <si>
+    <t>Número de irregularidades identificadas; processos encaminhados para apuração</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/55aa2a39-07ac-4906-b870-a0b977b8ca9b/530a839cc321a0407e62?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi</t>
+  </si>
+  <si>
+    <t>Painel de Monitoramento de Vistorias</t>
+  </si>
+  <si>
+    <t>Painel com indicadores operacionais e alertas de padrões suspeitos em laudos de vistoria e atuação de ECVs e vistoriadores, fortalecendo o controle e prevenção de fraudes.</t>
+  </si>
+  <si>
+    <t>Quantidade de alertas gerados; indicadores de vistoria monitorados</t>
+  </si>
+  <si>
+    <t>Coordenadoria de Segurança Veicular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/24666170-8ae6-404f-b4aa-a3f054f6f875/afcad7c632d95f0aeff7?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi
+</t>
+  </si>
+  <si>
+    <t>Automação de Transferência de Veículos</t>
+  </si>
+  <si>
+    <t>Ampliação da automação dos processos de transferência de veículos por meio do e-CRV e RENAVE, reduzindo intervenção manual e aumentando a eficiência administrativa.</t>
+  </si>
+  <si>
+    <t>Percentual de transferências automatizadas</t>
+  </si>
+  <si>
+    <t>Coordenadoria de Registro de Veículos</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/37783c04-f32e-4913-ae3f-d34ce6be6230/a7174c53064c71501d9e?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi</t>
+  </si>
+  <si>
+    <t>Automação de Primeiro Registro de Veículos</t>
+  </si>
+  <si>
+    <t>Implementação de processos automatizados para primeiro registro de veículos, permitindo emissão imediata do documento após conclusão do processo.</t>
+  </si>
+  <si>
+    <t>Percentual de registros automatizados</t>
+  </si>
+  <si>
+    <t>https://governosp.sharepoint.com/:x:/t/DETRAN-CoordenadoriadeSeguranaViria/IQD-XMzrwR9wQJRbCicTRUisAcIElcJAjtv72HyEZzywMiA?email=felipe.lucena%40detran.sp.gov.br&amp;e=jimoXx</t>
+  </si>
+  <si>
+    <t>Automação do Licenciamento</t>
+  </si>
+  <si>
+    <t>Ampliação da automação na emissão de licenciamento anual de veículos, reduzindo etapas administrativas e aumentando a eficiência do processo.</t>
+  </si>
+  <si>
+    <t>Percentual de licenciamento automatizado</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/37783c04-f32e-4913-ae3f-d34ce6be6230/6abb3d0350e2751b3a00?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi</t>
+  </si>
+  <si>
+    <t>Transformação Digital de Documentos Veiculares</t>
+  </si>
+  <si>
+    <t>Conversão de documentos veiculares físicos para formato digital, ampliando acesso eletrônico e reduzindo necessidade de atendimento presencial.</t>
+  </si>
+  <si>
+    <t>Quantidade de documentos digitalizados</t>
+  </si>
+  <si>
+    <t>70.300</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DQmQUF9AM2O/?igsh=MWd3cmF6Z3FwdzZ1aA%3D%3D</t>
+  </si>
+  <si>
+    <t>Cadastro Antecipado de Locais de Vistoria para Concessionárias RENAVE</t>
+  </si>
+  <si>
+    <t>Cadastro antecipado de postos de vistoria para concessionárias participantes do RENAVE, ampliando a capilaridade e capacidade de atendimento.</t>
+  </si>
+  <si>
+    <t>Quantidade de postos cadastrados</t>
+  </si>
+  <si>
+    <t>Coordenadora de Gestão do Mercado de Veículos e Autopartes</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/24666170-8ae6-404f-b4aa-a3f054f6f875/afcad7c632d95f0aeff7?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi</t>
+  </si>
+  <si>
+    <t>Gestão do Mercado de Desmontagem e Reciclagem de Veículos</t>
+  </si>
+  <si>
+    <t>Uso de painéis de dados e melhorias sistêmicas para monitoramento do mercado de peças e desmontagem de veículos.</t>
+  </si>
+  <si>
+    <t>Indicadores do mercado de peças e desmontes</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/2b910569-578e-46c3-a1fd-41f67be9a848/005fba4a9e7b963d3750?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi</t>
+  </si>
+  <si>
+    <t>Novo Sistema Estadual de Vistoria</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de novo sistema estadual de vistoria com objetivo de ampliar segurança, qualidade das inspeções e controle de fraudes.</t>
+  </si>
+  <si>
+    <t>Indicadores operacionais do sistema de vistoria</t>
+  </si>
+  <si>
+    <t>https://www.detran.sp.gov.br/detransp/pb/regulacao/normas/portaria-normativa-detran-sp-n%C2%BA-47-de-27-de-novembro-de?id=ver_norma&amp;sys_kb_id=ad81fb64fb61f6904f2afda46eefdc44</t>
+  </si>
+  <si>
+    <t>Transferência Digital de Veículos (TDV)</t>
+  </si>
+  <si>
+    <t>Monitoramento e aprimoramento do processo de transferência digital de veículos, com indicadores de desempenho e análise de dados operacionais.</t>
+  </si>
+  <si>
+    <t>Quantidade de TDVs processadas; tempo de processamento</t>
+  </si>
+  <si>
+    <t>https://app.powerbi.com/groups/me/apps/44e8b92a-0f2d-410a-ad47-d6b272aac3e6/reports/9150cd77-3b10-4e7d-935c-795b85ea2c5c/b0104f9e190bd4ff686b?ctid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;pane=help&amp;experience=power-bi</t>
+  </si>
+  <si>
+    <t>Dispensa de Vistoria em Serviços Específicos</t>
+  </si>
+  <si>
+    <t>Implementação de regra que dispensa vistoria em determinados serviços veiculares sem alteração do veículo, conforme Resolução Contran nº 941/2022.</t>
+  </si>
+  <si>
+    <t>Quantidade de serviços realizados sem vistoria</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>https://www.agenciasp.sp.gov.br/servicos-de-veiculos-do-detran-sp-passam-a-dispensar-vistoria-em-casos-especificos/</t>
+  </si>
+  <si>
+    <t>Jornada de Fiscalização de Licenciamento</t>
+  </si>
+  <si>
+    <t>Estratégia de fiscalização baseada em análise de dados da frota não licenciada, priorizando municípios com índices superiores à média estadual.</t>
+  </si>
+  <si>
+    <t>Percentual de frota não licenciada por município</t>
+  </si>
+  <si>
+    <t>https://planner.cloud.microsoft/webui/plan/O9OxbHCHR0aykTrHhUXPv2UAAkAn/view/board/task/h15em80Al0yqPoWMXrTh9mUAOHft?tid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;PlannerRouteHint=3a78b0cd-7c8e-4929-83d5-190a6cc01365</t>
+  </si>
+  <si>
+    <t>Registro de Sinistro de Trânsito (RST)</t>
+  </si>
+  <si>
+    <t>Ferramenta digital para comunicação de acidentes de trânsito sem vítimas por cidadãos, conforme diretrizes da Resolução CONTRAN nº 810/2020.</t>
+  </si>
+  <si>
+    <t>Quantidade de registros de sinistros realizados</t>
+  </si>
+  <si>
+    <t>https://planner.cloud.microsoft/webui/plan/ZjdcxcVZDk6P0scFRHDtkWUAD11Z/view/board/task/IQeRROy0f0aVDN3YgnHrGmUANJ9v?tid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;PlannerRouteHint=3a78b0cd-7c8e-4929-83d5-190a6cc01365</t>
+  </si>
+  <si>
+    <t>Indicador de Alterações de Características (DCC)</t>
+  </si>
+  <si>
+    <t>Criação de indicador analítico para consolidação e monitoramento das autorizações de alterações de características de veículos.</t>
+  </si>
+  <si>
+    <t>Quantidade de autorizações analisadas por tipo de alteração</t>
+  </si>
+  <si>
+    <t>https://planner.cloud.microsoft/webui/plan/ZjdcxcVZDk6P0scFRHDtkWUAD11Z/view/board/task/BsAXoEeaEUmySwOs2TYTT2UAGHS1?tid=3a78b0cd-7c8e-4929-83d5-190a6cc01365&amp;PlannerRouteHint=3a78b0cd-7c8e-4929-83d5-190a6cc01365</t>
+  </si>
+  <si>
+    <t>Portaria Normativa DETRAN-SP nº 39</t>
+  </si>
+  <si>
+    <t>Estabelece normas e procedimentos para o emplacamento de veículos e atuação das empresas estampadoras de placas no Estado de São Paulo.</t>
+  </si>
+  <si>
+    <t>https://www.doe.sp.gov.br/executivo/secretaria-de-gestao-e-governo-digital/portaria-normativa-detran-sp-n-39-de-12-de-marco-de-2025-20250312112817215941826</t>
+  </si>
+  <si>
+    <t>Portaria Normativa DETRAN-SP nº 41</t>
+  </si>
+  <si>
+    <t>Regulamenta procedimentos para registro de contratos de financiamento com garantia real de veículo e execução extrajudicial no Estado de São Paulo.</t>
+  </si>
+  <si>
+    <t>https://www.doe.sp.gov.br/executivo/secretaria-de-gestao-e-governo-digital/portaria-normativa-detran-sp-n-41-de-15-de-abril-de-2025-202504151128192151021390</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -500,179 +785,206 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="67">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+  <dxfs count="73">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -727,10 +1039,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:BQ7" totalsRowShown="0">
-  <autoFilter ref="A1:BQ7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="69">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:BW25" totalsRowShown="0">
+  <autoFilter ref="A1:BW25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="75">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="72">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -751,437 +1063,479 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="65">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="71">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="64">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nome" dataDxfId="70">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Sua diretoria" dataDxfId="63">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Sua diretoria" dataDxfId="69">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5d0166562107401e991954416e356874"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tipo de produto a ser enviado" dataDxfId="62">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Tipo de produto a ser enviado" dataDxfId="68">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r628572c0e3c047489c312c92fb4c055d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Pilar" dataDxfId="61">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Pilar" dataDxfId="67">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5acc97b770c54696957fa2032e70d8ee"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Ação" dataDxfId="60">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Ação" dataDxfId="66">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r04fa67349c664e21bfb59f8ac7badf90"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Produto" dataDxfId="59">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Produto" dataDxfId="65">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9491ca7f41ee47ffaa370286408a2095"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Título do produto Detran" dataDxfId="58">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Título do produto Detran" dataDxfId="64">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8c8a3f80c30a4d52b77174cedc9da892"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Descrição e justificativa" dataDxfId="57">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Descrição e justificativa" dataDxfId="63">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5fc6e286c90b4d82abab78e37adcdb9b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Indicador" dataDxfId="56">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Indicador" dataDxfId="62">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r862e64a335b74091a120b52ab69bc3df"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ano referência" dataDxfId="55">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Ano referência" dataDxfId="61">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r8424abcba0b44b20af65d0da32d00edd"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Valor resultado" dataDxfId="54">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Valor resultado" dataDxfId="60">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r462a59a1b9864908be2d8da5d84760a5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Área responsável" dataDxfId="53">
+    <tableColumn id="70" xr3:uid="{CFD71CBB-E82C-4C83-A1A4-D60AD5D1D4B4}" name="Observações" dataDxfId="59">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r9795dc44096c453e9fddadb14bea4cc7"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Área responsável" dataDxfId="58">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rca669805af6c4a7996b60ab4fa682fd1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Links comprovatórios" dataDxfId="52">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Links comprovatórios" dataDxfId="57">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd578f575744f4f5cb4222b051510b6a4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Arquivos comprovatórios" dataDxfId="51">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Arquivos comprovatórios" dataDxfId="56">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r855ee4d4536e4bce9c07e2aff8d04b4f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Ação1" dataDxfId="50">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Ação1" dataDxfId="55">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r572b2fc07b334df4ae1854b4ff0a52b8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Produto1" dataDxfId="49">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Produto1" dataDxfId="54">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r57f167fb699c47aaa30b5f7d7f3bc9b7"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Título do produto Detran1" dataDxfId="48">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Título do produto Detran1" dataDxfId="53">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5acd677bf86d424b9871d79926a22f88"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Descrição e justificativa1" dataDxfId="47">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Descrição e justificativa1" dataDxfId="52">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r53e4277c091e406fadd1a991205013eb"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Indicador1" dataDxfId="46">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Indicador1" dataDxfId="51">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r624067ec44404e8987c10d5b4249982d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Ano referência1" dataDxfId="45">
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Ano referência1" dataDxfId="50">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r05ec762726cb4df4b70e217158c6e86b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Valor resultado1" dataDxfId="44">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Valor resultado1" dataDxfId="49">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="recce438b3c914a87bacaadc77f772753"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Área responsável1" dataDxfId="43">
+    <tableColumn id="71" xr3:uid="{5D80E050-0BF7-4996-A090-97BF6BB70740}" name="Observações1" dataDxfId="48">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r54fc8905430343a3a29773e556c75c35"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Área responsável1" dataDxfId="47">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb3bd41171da24efe8613495c63b24b8b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Links comprovatórios1" dataDxfId="42">
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Links comprovatórios1" dataDxfId="46">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9308fc56649b4f08b3f53d909b19f505"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Arquivos comprovatórios1" dataDxfId="41">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Arquivos comprovatórios1" dataDxfId="45">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r4ce01a5da84349f99d576dd54d8f2e96"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Ação2" dataDxfId="40">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Ação2" dataDxfId="44">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6fdaa8d73e5342aa85d370a6727b8bcc"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Produto2" dataDxfId="39">
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Produto2" dataDxfId="43">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r95b0f5237f8b4338a0121bcd1dd5532d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Título do produto Detran2" dataDxfId="38">
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Título do produto Detran2" dataDxfId="42">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r539c3327f4d44704a7d924bd30ec4992"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Descrição e justificativa2" dataDxfId="37">
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Descrição e justificativa2" dataDxfId="41">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r70ddeb253c414e73a1dde4cefa1c7070"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Indicador2" dataDxfId="36">
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Indicador2" dataDxfId="40">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r139dd00e502d43bb8f46ce6f1830e598"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Ano referência2" dataDxfId="35">
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="Ano referência2" dataDxfId="39">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r2559553af70a4c8c913a09e681318a0d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Valor resultado2" dataDxfId="34">
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="Valor resultado2" dataDxfId="38">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r62b47862fef24db8a94897ae30e16818"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Área responsável2" dataDxfId="33">
+    <tableColumn id="72" xr3:uid="{4E3940D9-F3D3-4919-9FDB-066FAE97C55C}" name="Observações2" dataDxfId="37">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r0db7ff3db81748cb9040271b8262904d"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0000-000024000000}" name="Área responsável2" dataDxfId="36">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="raae9848a2c53478092bfeca58096e1e0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Links comprovatórios2" dataDxfId="32">
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0000-000025000000}" name="Links comprovatórios2" dataDxfId="35">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9bd6dcd2a3a648bda4c7f6c3fb997e1f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Arquivos comprovatórios2" dataDxfId="31">
+    <tableColumn id="38" xr3:uid="{00000000-0010-0000-0000-000026000000}" name="Arquivos comprovatórios2" dataDxfId="34">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r4f5b2eb15e9a48a5b17a99d4b51a90a0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Em caso de dúvidas, acesse o documento base:" dataDxfId="30">
+    <tableColumn id="39" xr3:uid="{00000000-0010-0000-0000-000027000000}" name="Em caso de dúvidas, acesse o documento base:" dataDxfId="33">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r56a3f4a69d194daaaaa871fca26726ff"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Ação3" dataDxfId="29">
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="Ação3" dataDxfId="32">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rdac09ae4bb0f47b9b64f7710fc83becc"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Produto3" dataDxfId="28">
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0000-000029000000}" name="Produto3" dataDxfId="31">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r17cb70ab3a1b4255a9423f70335e24fb"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Título do produto Detran3" dataDxfId="27">
+    <tableColumn id="42" xr3:uid="{00000000-0010-0000-0000-00002A000000}" name="Título do produto Detran3" dataDxfId="30">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc77afee4b7374e578cabd9f550e79436"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Descrição e justificativa3" dataDxfId="26">
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Descrição e justificativa3" dataDxfId="29">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9252d9c914ca402bbc5fd76a95868724"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Indicador3" dataDxfId="25">
+    <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="Indicador3" dataDxfId="28">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc10ddf5294b64cd6a14bc3bf6ae08c2a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Ano referência3" dataDxfId="24">
+    <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="Ano referência3" dataDxfId="27">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rdfccf2f1e3f64fd2b4096f4b760dc5eb"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Valor resultado3" dataDxfId="23">
+    <tableColumn id="73" xr3:uid="{F58023C8-7E1B-4A9F-A0BE-C6B95E06CB59}" name="Observações3" dataDxfId="26">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r837be42298684cedba5918b9e0913cf7"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="Valor resultado3" dataDxfId="25">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rbb2e218f6eff498c9bcc1c930139f80d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Área responsável3" dataDxfId="22">
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="Área responsável3" dataDxfId="24">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7845d5ec065d43cba34bc51fe9fdf8d6"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Links comprovatórios3" dataDxfId="21">
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="Links comprovatórios3" dataDxfId="23">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r89a39eb74ff846fb9dbf761745df88ce"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Arquivos comprovatórios3" dataDxfId="20">
+    <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="Arquivos comprovatórios3" dataDxfId="22">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r279f342fdeb345b6ae8301859c78e1c4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="Ação4" dataDxfId="19">
+    <tableColumn id="50" xr3:uid="{00000000-0010-0000-0000-000032000000}" name="Ação4" dataDxfId="21">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc653cf6343934c9f85cdc273993ce600"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Produto4" dataDxfId="18">
+    <tableColumn id="51" xr3:uid="{00000000-0010-0000-0000-000033000000}" name="Produto4" dataDxfId="20">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r05dfc0553cc848e8ac79a317bf5ff45b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Título do produto Detran4" dataDxfId="17">
+    <tableColumn id="52" xr3:uid="{00000000-0010-0000-0000-000034000000}" name="Título do produto Detran4" dataDxfId="19">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re39620704eca4e469c25667913819c1c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="Descrição e justificativa4" dataDxfId="16">
+    <tableColumn id="53" xr3:uid="{00000000-0010-0000-0000-000035000000}" name="Descrição e justificativa4" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7beaaa5fb4ad4a0ba223ea319a4a8a16"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Indicador4" dataDxfId="15">
+    <tableColumn id="54" xr3:uid="{00000000-0010-0000-0000-000036000000}" name="Indicador4" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r636384e2371e47a084e5973d2d622ac4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Ano referência4" dataDxfId="14">
+    <tableColumn id="55" xr3:uid="{00000000-0010-0000-0000-000037000000}" name="Ano referência4" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc633211e25334bbfa43131ba4cb39b82"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Valor resultado4" dataDxfId="13">
+    <tableColumn id="74" xr3:uid="{B091AE93-A0AF-4E25-B89E-B8FC618724C0}" name="Observações4" dataDxfId="15">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r8ea7c639403d45739c1f2b287e7d8ae2"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="56" xr3:uid="{00000000-0010-0000-0000-000038000000}" name="Valor resultado4" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0fd0b8e590454f73ab8dcf6a4e9e7908"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Área responsável4" dataDxfId="12">
+    <tableColumn id="57" xr3:uid="{00000000-0010-0000-0000-000039000000}" name="Área responsável4" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf6c8f2cbe7f24c19a5d87824addc486e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Links comprovatórios4" dataDxfId="11">
+    <tableColumn id="58" xr3:uid="{00000000-0010-0000-0000-00003A000000}" name="Links comprovatórios4" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7f5e9d5caf1f4f3ebf3c820d9a8e770c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Arquivos comprovatórios4" dataDxfId="10">
+    <tableColumn id="59" xr3:uid="{00000000-0010-0000-0000-00003B000000}" name="Arquivos comprovatórios4" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9a4429c88f3343deb3e0face879a4021"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Ação5" dataDxfId="9">
+    <tableColumn id="60" xr3:uid="{00000000-0010-0000-0000-00003C000000}" name="Ação5" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5559142e30b94253ab806aef43c4a899"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Produto5" dataDxfId="8">
+    <tableColumn id="61" xr3:uid="{00000000-0010-0000-0000-00003D000000}" name="Produto5" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc717939c6b094d139ea9004b8231957e"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="Título do produto Detran5" dataDxfId="7">
+    <tableColumn id="62" xr3:uid="{00000000-0010-0000-0000-00003E000000}" name="Título do produto Detran5" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r90bcb78c17b244feafbba749b3bc10d5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="Descrição e justificativa5" dataDxfId="6">
+    <tableColumn id="63" xr3:uid="{00000000-0010-0000-0000-00003F000000}" name="Descrição e justificativa5" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="redad16a2f0b54c0cba729e3ccfd82b31"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="Indicador5" dataDxfId="5">
+    <tableColumn id="64" xr3:uid="{00000000-0010-0000-0000-000040000000}" name="Indicador5" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rdaa61c24c59f4f2eb73bb57e6b0be894"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="Ano referência5" dataDxfId="4">
+    <tableColumn id="65" xr3:uid="{00000000-0010-0000-0000-000041000000}" name="Ano referência5" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc5c1cf03ee254fed815966b1a998b222"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="75" xr3:uid="{5014C22A-A147-4403-8E2E-14FFB2E44662}" name="Observações5" dataDxfId="4">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r895fa22c3a584010b024b48516293f91"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -1217,7 +1571,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zbB4Oo58KUmD1RkKbMATZUorVdw7vntHqCx1Y9VzVMVUQ09JREFTMENQSUdSTjhVSjVRQTJEUTI5VSQlQCN0PWcu" isFormConnected="1" maxResponseId="6" latestEventMarker="0">
+      <xlmsforms:msForm id="zbB4Oo58KUmD1RkKbMATZUorVdw7vntHqCx1Y9VzVMVUQ09JREFTMENQSUdSTjhVSjVRQTJEUTI5VSQlQCN0PWcu" isFormConnected="1" maxResponseId="24" latestEventMarker="46">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1287,6 +1641,12 @@
         <xlmsforms:syncedQuestionId>r30f5af5f500146b5b569ff6a889e6e4e</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r357c512fe74c4468bd73f099fc208307</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r23aa4ad2956a4b92bd21681bef19fd28</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r9795dc44096c453e9fddadb14bea4cc7</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r54fc8905430343a3a29773e556c75c35</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r0db7ff3db81748cb9040271b8262904d</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r837be42298684cedba5918b9e0913cf7</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r8ea7c639403d45739c1f2b287e7d8ae2</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r895fa22c3a584010b024b48516293f91</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -1590,80 +1950,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BQ7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BW25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="80" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="70.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="71.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="70.21875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="77.88671875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="119.5546875" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19" customWidth="1"/>
+    <col min="17" max="17" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="71.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19" customWidth="1"/>
+    <col min="28" max="28" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19" customWidth="1"/>
+    <col min="39" max="39" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19" customWidth="1"/>
+    <col min="50" max="50" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19" customWidth="1"/>
+    <col min="61" max="61" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="119.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1871,8 +2233,26 @@
       <c r="BQ1" t="s">
         <v>68</v>
       </c>
+      <c r="BR1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1883,49 +2263,50 @@
         <v>46049.367268518516</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="P2" t="s">
-        <v>81</v>
-      </c>
-      <c r="R2" t="s">
-        <v>82</v>
+        <v>86</v>
+      </c>
+      <c r="P2" s="1"/>
+      <c r="Q2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1936,49 +2317,50 @@
         <v>46049.368252314816</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
-      </c>
-      <c r="S3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="T3" t="s">
+        <v>90</v>
+      </c>
+      <c r="U3" t="s">
+        <v>91</v>
+      </c>
+      <c r="V3" t="s">
+        <v>92</v>
+      </c>
+      <c r="W3" t="s">
+        <v>93</v>
+      </c>
+      <c r="X3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="U3" t="s">
-        <v>86</v>
-      </c>
-      <c r="V3" t="s">
-        <v>87</v>
-      </c>
-      <c r="W3" t="s">
-        <v>88</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>90</v>
+      <c r="Z3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA3" s="1"/>
+      <c r="AB3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1989,49 +2371,50 @@
         <v>46049.380393518521</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>93</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AQ4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AR4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT4" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>101</v>
       </c>
       <c r="AU4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>99</v>
+        <v>102</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW4" s="1"/>
+      <c r="AX4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2042,52 +2425,53 @@
         <v>46049.384247685186</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>101</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>102</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>103</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>104</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>105</v>
-      </c>
-      <c r="BM5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN5" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="BM5" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>108</v>
+      </c>
       <c r="BO5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BP5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BQ5" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="BR5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="BS5" s="1"/>
+      <c r="BT5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>113</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>114</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2098,49 +2482,50 @@
         <v>46049.387916666667</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="P6" t="s">
-        <v>71</v>
-      </c>
-      <c r="R6" t="s">
-        <v>117</v>
+        <v>122</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" t="s">
+        <v>77</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2151,58 +2536,1986 @@
         <v>46049.392939814818</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AN7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>124</v>
+      </c>
+      <c r="AR7" t="s">
         <v>118</v>
       </c>
-      <c r="AO7" t="s">
-        <v>112</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>119</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>120</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>121</v>
-      </c>
-      <c r="AS7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT7" s="1" t="s">
-        <v>89</v>
+      <c r="AS7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>126</v>
       </c>
       <c r="AU7" t="s">
-        <v>71</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>122</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="AV7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>77</v>
+      </c>
+      <c r="BA7" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46085.464560185203</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46085.466979166697</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF8" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI8" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AJ8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK8" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM8" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="4"/>
+      <c r="AR8" s="4"/>
+      <c r="AS8" s="4"/>
+      <c r="AT8" s="4"/>
+      <c r="AU8" s="4"/>
+      <c r="AV8" s="5"/>
+      <c r="AW8" s="1"/>
+      <c r="AX8" s="5"/>
+      <c r="AY8" s="4"/>
+      <c r="AZ8" s="4"/>
+      <c r="BA8" s="4"/>
+      <c r="BB8" s="4"/>
+      <c r="BC8" s="4"/>
+      <c r="BD8" s="4"/>
+      <c r="BE8" s="4"/>
+      <c r="BF8" s="4"/>
+      <c r="BG8" s="4"/>
+      <c r="BI8" s="4"/>
+      <c r="BJ8" s="4"/>
+      <c r="BK8" s="4"/>
+      <c r="BL8" s="4"/>
+      <c r="BM8" s="4"/>
+      <c r="BN8" s="4"/>
+      <c r="BO8" s="4"/>
+      <c r="BP8" s="4"/>
+      <c r="BQ8" s="4"/>
+      <c r="BR8" s="4"/>
+      <c r="BT8" s="4"/>
+      <c r="BU8" s="4"/>
+      <c r="BV8" s="4"/>
+      <c r="BW8" s="4"/>
+    </row>
+    <row r="9" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46091.7104398148</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46091.7120138889</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG9" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH9" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="AI9" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM9" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN9" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO9" s="4"/>
+      <c r="AP9" s="4"/>
+      <c r="AQ9" s="4"/>
+      <c r="AR9" s="4"/>
+      <c r="AS9" s="4"/>
+      <c r="AT9" s="4"/>
+      <c r="AU9" s="4"/>
+      <c r="AV9" s="5"/>
+      <c r="AW9" s="1"/>
+      <c r="AX9" s="5"/>
+      <c r="AY9" s="4"/>
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+      <c r="BB9" s="4"/>
+      <c r="BC9" s="4"/>
+      <c r="BD9" s="4"/>
+      <c r="BE9" s="4"/>
+      <c r="BF9" s="4"/>
+      <c r="BG9" s="4"/>
+      <c r="BI9" s="4"/>
+      <c r="BJ9" s="4"/>
+      <c r="BK9" s="4"/>
+      <c r="BL9" s="4"/>
+      <c r="BM9" s="4"/>
+      <c r="BN9" s="4"/>
+      <c r="BO9" s="4"/>
+      <c r="BP9" s="4"/>
+      <c r="BQ9" s="4"/>
+      <c r="BR9" s="4"/>
+      <c r="BT9" s="4"/>
+      <c r="BU9" s="4"/>
+      <c r="BV9" s="4"/>
+      <c r="BW9" s="4"/>
+    </row>
+    <row r="10" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46091.712048611102</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46091.712673611102</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG10" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH10" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="AI10" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="AJ10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK10" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM10" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN10" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AO10" s="4"/>
+      <c r="AP10" s="4"/>
+      <c r="AQ10" s="4"/>
+      <c r="AR10" s="4"/>
+      <c r="AS10" s="4"/>
+      <c r="AT10" s="4"/>
+      <c r="AU10" s="4"/>
+      <c r="AV10" s="5"/>
+      <c r="AW10" s="1"/>
+      <c r="AX10" s="5"/>
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="4"/>
+      <c r="BA10" s="4"/>
+      <c r="BB10" s="4"/>
+      <c r="BC10" s="4"/>
+      <c r="BD10" s="4"/>
+      <c r="BE10" s="4"/>
+      <c r="BF10" s="4"/>
+      <c r="BG10" s="4"/>
+      <c r="BI10" s="4"/>
+      <c r="BJ10" s="4"/>
+      <c r="BK10" s="4"/>
+      <c r="BL10" s="4"/>
+      <c r="BM10" s="4"/>
+      <c r="BN10" s="4"/>
+      <c r="BO10" s="4"/>
+      <c r="BP10" s="4"/>
+      <c r="BQ10" s="4"/>
+      <c r="BR10" s="4"/>
+      <c r="BT10" s="4"/>
+      <c r="BU10" s="4"/>
+      <c r="BV10" s="4"/>
+      <c r="BW10" s="4"/>
+    </row>
+    <row r="11" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46091.712754629603</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46091.713310185201</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG11" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AH11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AI11" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM11" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN11" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
+      <c r="AQ11" s="4"/>
+      <c r="AR11" s="4"/>
+      <c r="AS11" s="4"/>
+      <c r="AT11" s="4"/>
+      <c r="AU11" s="4"/>
+      <c r="AV11" s="5"/>
+      <c r="AW11" s="1"/>
+      <c r="AX11" s="5"/>
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4"/>
+      <c r="BA11" s="4"/>
+      <c r="BB11" s="4"/>
+      <c r="BC11" s="4"/>
+      <c r="BD11" s="4"/>
+      <c r="BE11" s="4"/>
+      <c r="BF11" s="4"/>
+      <c r="BG11" s="4"/>
+      <c r="BI11" s="4"/>
+      <c r="BJ11" s="4"/>
+      <c r="BK11" s="4"/>
+      <c r="BL11" s="4"/>
+      <c r="BM11" s="4"/>
+      <c r="BN11" s="4"/>
+      <c r="BO11" s="4"/>
+      <c r="BP11" s="4"/>
+      <c r="BQ11" s="4"/>
+      <c r="BR11" s="4"/>
+      <c r="BT11" s="4"/>
+      <c r="BU11" s="4"/>
+      <c r="BV11" s="4"/>
+      <c r="BW11" s="4"/>
+    </row>
+    <row r="12" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46091.7133680556</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46091.713935185202</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG12" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AH12" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI12" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="AJ12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK12" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM12" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN12" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
+      <c r="AQ12" s="4"/>
+      <c r="AR12" s="4"/>
+      <c r="AS12" s="4"/>
+      <c r="AT12" s="4"/>
+      <c r="AU12" s="4"/>
+      <c r="AV12" s="5"/>
+      <c r="AW12" s="1"/>
+      <c r="AX12" s="5"/>
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="4"/>
+      <c r="BA12" s="4"/>
+      <c r="BB12" s="4"/>
+      <c r="BC12" s="4"/>
+      <c r="BD12" s="4"/>
+      <c r="BE12" s="4"/>
+      <c r="BF12" s="4"/>
+      <c r="BG12" s="4"/>
+      <c r="BI12" s="4"/>
+      <c r="BJ12" s="4"/>
+      <c r="BK12" s="4"/>
+      <c r="BL12" s="4"/>
+      <c r="BM12" s="4"/>
+      <c r="BN12" s="4"/>
+      <c r="BO12" s="4"/>
+      <c r="BP12" s="4"/>
+      <c r="BQ12" s="4"/>
+      <c r="BR12" s="4"/>
+      <c r="BT12" s="4"/>
+      <c r="BU12" s="4"/>
+      <c r="BV12" s="4"/>
+      <c r="BW12" s="4"/>
+    </row>
+    <row r="13" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46091.713958333297</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46091.714513888903</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG13" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH13" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="AI13" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM13" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN13" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="4"/>
+      <c r="AQ13" s="4"/>
+      <c r="AR13" s="4"/>
+      <c r="AS13" s="4"/>
+      <c r="AT13" s="4"/>
+      <c r="AU13" s="4"/>
+      <c r="AV13" s="5"/>
+      <c r="AW13" s="1"/>
+      <c r="AX13" s="5"/>
+      <c r="AY13" s="4"/>
+      <c r="AZ13" s="4"/>
+      <c r="BA13" s="4"/>
+      <c r="BB13" s="4"/>
+      <c r="BC13" s="4"/>
+      <c r="BD13" s="4"/>
+      <c r="BE13" s="4"/>
+      <c r="BF13" s="4"/>
+      <c r="BG13" s="4"/>
+      <c r="BI13" s="4"/>
+      <c r="BJ13" s="4"/>
+      <c r="BK13" s="4"/>
+      <c r="BL13" s="4"/>
+      <c r="BM13" s="4"/>
+      <c r="BN13" s="4"/>
+      <c r="BO13" s="4"/>
+      <c r="BP13" s="4"/>
+      <c r="BQ13" s="4"/>
+      <c r="BR13" s="4"/>
+      <c r="BT13" s="4"/>
+      <c r="BU13" s="4"/>
+      <c r="BV13" s="4"/>
+      <c r="BW13" s="4"/>
+    </row>
+    <row r="14" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46091.714525463001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46091.715092592603</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG14" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="AH14" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="AI14" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK14" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM14" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN14" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AO14" s="4"/>
+      <c r="AP14" s="4"/>
+      <c r="AQ14" s="4"/>
+      <c r="AR14" s="4"/>
+      <c r="AS14" s="4"/>
+      <c r="AT14" s="4"/>
+      <c r="AU14" s="4"/>
+      <c r="AV14" s="5"/>
+      <c r="AW14" s="1"/>
+      <c r="AX14" s="5"/>
+      <c r="AY14" s="4"/>
+      <c r="AZ14" s="4"/>
+      <c r="BA14" s="4"/>
+      <c r="BB14" s="4"/>
+      <c r="BC14" s="4"/>
+      <c r="BD14" s="4"/>
+      <c r="BE14" s="4"/>
+      <c r="BF14" s="4"/>
+      <c r="BG14" s="4"/>
+      <c r="BI14" s="4"/>
+      <c r="BJ14" s="4"/>
+      <c r="BK14" s="4"/>
+      <c r="BL14" s="4"/>
+      <c r="BM14" s="4"/>
+      <c r="BN14" s="4"/>
+      <c r="BO14" s="4"/>
+      <c r="BP14" s="4"/>
+      <c r="BQ14" s="4"/>
+      <c r="BR14" s="4"/>
+      <c r="BT14" s="4"/>
+      <c r="BU14" s="4"/>
+      <c r="BV14" s="4"/>
+      <c r="BW14" s="4"/>
+    </row>
+    <row r="15" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46091.715115740699</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46091.7160532407</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH15" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AI15" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK15" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="AM15" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN15" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="AO15" s="4"/>
+      <c r="AP15" s="4"/>
+      <c r="AQ15" s="4"/>
+      <c r="AR15" s="4"/>
+      <c r="AS15" s="4"/>
+      <c r="AT15" s="4"/>
+      <c r="AU15" s="4"/>
+      <c r="AV15" s="5"/>
+      <c r="AW15" s="1"/>
+      <c r="AX15" s="5"/>
+      <c r="AY15" s="4"/>
+      <c r="AZ15" s="4"/>
+      <c r="BA15" s="4"/>
+      <c r="BB15" s="4"/>
+      <c r="BC15" s="4"/>
+      <c r="BD15" s="4"/>
+      <c r="BE15" s="4"/>
+      <c r="BF15" s="4"/>
+      <c r="BG15" s="4"/>
+      <c r="BI15" s="4"/>
+      <c r="BJ15" s="4"/>
+      <c r="BK15" s="4"/>
+      <c r="BL15" s="4"/>
+      <c r="BM15" s="4"/>
+      <c r="BN15" s="4"/>
+      <c r="BO15" s="4"/>
+      <c r="BP15" s="4"/>
+      <c r="BQ15" s="4"/>
+      <c r="BR15" s="4"/>
+      <c r="BT15" s="4"/>
+      <c r="BU15" s="4"/>
+      <c r="BV15" s="4"/>
+      <c r="BW15" s="4"/>
+    </row>
+    <row r="16" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46091.716099537</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46091.716643518499</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AB16" s="4"/>
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="4"/>
+      <c r="AE16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG16" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="AH16" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI16" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM16" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AN16" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AO16" s="4"/>
+      <c r="AP16" s="4"/>
+      <c r="AQ16" s="4"/>
+      <c r="AR16" s="4"/>
+      <c r="AS16" s="4"/>
+      <c r="AT16" s="4"/>
+      <c r="AU16" s="4"/>
+      <c r="AV16" s="5"/>
+      <c r="AW16" s="1"/>
+      <c r="AX16" s="5"/>
+      <c r="AY16" s="4"/>
+      <c r="AZ16" s="4"/>
+      <c r="BA16" s="4"/>
+      <c r="BB16" s="4"/>
+      <c r="BC16" s="4"/>
+      <c r="BD16" s="4"/>
+      <c r="BE16" s="4"/>
+      <c r="BF16" s="4"/>
+      <c r="BG16" s="4"/>
+      <c r="BI16" s="4"/>
+      <c r="BJ16" s="4"/>
+      <c r="BK16" s="4"/>
+      <c r="BL16" s="4"/>
+      <c r="BM16" s="4"/>
+      <c r="BN16" s="4"/>
+      <c r="BO16" s="4"/>
+      <c r="BP16" s="4"/>
+      <c r="BQ16" s="4"/>
+      <c r="BR16" s="4"/>
+      <c r="BT16" s="4"/>
+      <c r="BU16" s="4"/>
+      <c r="BV16" s="4"/>
+      <c r="BW16" s="4"/>
+    </row>
+    <row r="17" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46091.716655092598</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46091.717187499999</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG17" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="AH17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI17" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AJ17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM17" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AN17" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="4"/>
+      <c r="AQ17" s="4"/>
+      <c r="AR17" s="4"/>
+      <c r="AS17" s="4"/>
+      <c r="AT17" s="4"/>
+      <c r="AU17" s="4"/>
+      <c r="AV17" s="5"/>
+      <c r="AW17" s="1"/>
+      <c r="AX17" s="5"/>
+      <c r="AY17" s="4"/>
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="4"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="4"/>
+      <c r="BD17" s="4"/>
+      <c r="BE17" s="4"/>
+      <c r="BF17" s="4"/>
+      <c r="BG17" s="4"/>
+      <c r="BI17" s="4"/>
+      <c r="BJ17" s="4"/>
+      <c r="BK17" s="4"/>
+      <c r="BL17" s="4"/>
+      <c r="BM17" s="4"/>
+      <c r="BN17" s="4"/>
+      <c r="BO17" s="4"/>
+      <c r="BP17" s="4"/>
+      <c r="BQ17" s="4"/>
+      <c r="BR17" s="4"/>
+      <c r="BT17" s="4"/>
+      <c r="BU17" s="4"/>
+      <c r="BV17" s="4"/>
+      <c r="BW17" s="4"/>
+    </row>
+    <row r="18" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46091.7172685185</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46091.717800925901</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG18" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="AH18" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI18" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="AJ18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM18" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN18" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="AO18" s="4"/>
+      <c r="AP18" s="4"/>
+      <c r="AQ18" s="4"/>
+      <c r="AR18" s="4"/>
+      <c r="AS18" s="4"/>
+      <c r="AT18" s="4"/>
+      <c r="AU18" s="4"/>
+      <c r="AV18" s="5"/>
+      <c r="AW18" s="1"/>
+      <c r="AX18" s="5"/>
+      <c r="AY18" s="4"/>
+      <c r="AZ18" s="4"/>
+      <c r="BA18" s="4"/>
+      <c r="BB18" s="4"/>
+      <c r="BC18" s="4"/>
+      <c r="BD18" s="4"/>
+      <c r="BE18" s="4"/>
+      <c r="BF18" s="4"/>
+      <c r="BG18" s="4"/>
+      <c r="BI18" s="4"/>
+      <c r="BJ18" s="4"/>
+      <c r="BK18" s="4"/>
+      <c r="BL18" s="4"/>
+      <c r="BM18" s="4"/>
+      <c r="BN18" s="4"/>
+      <c r="BO18" s="4"/>
+      <c r="BP18" s="4"/>
+      <c r="BQ18" s="4"/>
+      <c r="BR18" s="4"/>
+      <c r="BT18" s="4"/>
+      <c r="BU18" s="4"/>
+      <c r="BV18" s="4"/>
+      <c r="BW18" s="4"/>
+    </row>
+    <row r="19" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46091.717824074098</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46091.718414351897</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG19" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH19" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="AI19" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="AJ19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK19" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM19" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN19" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="AO19" s="4"/>
+      <c r="AP19" s="4"/>
+      <c r="AQ19" s="4"/>
+      <c r="AR19" s="4"/>
+      <c r="AS19" s="4"/>
+      <c r="AT19" s="4"/>
+      <c r="AU19" s="4"/>
+      <c r="AV19" s="5"/>
+      <c r="AW19" s="1"/>
+      <c r="AX19" s="5"/>
+      <c r="AY19" s="4"/>
+      <c r="AZ19" s="4"/>
+      <c r="BA19" s="4"/>
+      <c r="BB19" s="4"/>
+      <c r="BC19" s="4"/>
+      <c r="BD19" s="4"/>
+      <c r="BE19" s="4"/>
+      <c r="BF19" s="4"/>
+      <c r="BG19" s="4"/>
+      <c r="BI19" s="4"/>
+      <c r="BJ19" s="4"/>
+      <c r="BK19" s="4"/>
+      <c r="BL19" s="4"/>
+      <c r="BM19" s="4"/>
+      <c r="BN19" s="4"/>
+      <c r="BO19" s="4"/>
+      <c r="BP19" s="4"/>
+      <c r="BQ19" s="4"/>
+      <c r="BR19" s="4"/>
+      <c r="BT19" s="4"/>
+      <c r="BU19" s="4"/>
+      <c r="BV19" s="4"/>
+      <c r="BW19" s="4"/>
+    </row>
+    <row r="20" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46091.7184375</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46091.719074074099</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="4"/>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="4"/>
+      <c r="AD20" s="4"/>
+      <c r="AE20" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG20" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="AH20" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI20" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="AJ20" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="AK20" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN20" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO20" s="4"/>
+      <c r="AP20" s="4"/>
+      <c r="AQ20" s="4"/>
+      <c r="AR20" s="4"/>
+      <c r="AS20" s="4"/>
+      <c r="AT20" s="4"/>
+      <c r="AU20" s="4"/>
+      <c r="AV20" s="5"/>
+      <c r="AW20" s="1"/>
+      <c r="AX20" s="5"/>
+      <c r="AY20" s="4"/>
+      <c r="AZ20" s="4"/>
+      <c r="BA20" s="4"/>
+      <c r="BB20" s="4"/>
+      <c r="BC20" s="4"/>
+      <c r="BD20" s="4"/>
+      <c r="BE20" s="4"/>
+      <c r="BF20" s="4"/>
+      <c r="BG20" s="4"/>
+      <c r="BI20" s="4"/>
+      <c r="BJ20" s="4"/>
+      <c r="BK20" s="4"/>
+      <c r="BL20" s="4"/>
+      <c r="BM20" s="4"/>
+      <c r="BN20" s="4"/>
+      <c r="BO20" s="4"/>
+      <c r="BP20" s="4"/>
+      <c r="BQ20" s="4"/>
+      <c r="BR20" s="4"/>
+      <c r="BT20" s="4"/>
+      <c r="BU20" s="4"/>
+      <c r="BV20" s="4"/>
+      <c r="BW20" s="4"/>
+    </row>
+    <row r="21" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46091.7191087963</v>
+      </c>
+      <c r="C21" s="2">
+        <v>46091.719687500001</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="4"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF21" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG21" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AH21" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="AI21" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AJ21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM21" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN21" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="AO21" s="4"/>
+      <c r="AP21" s="4"/>
+      <c r="AQ21" s="4"/>
+      <c r="AR21" s="4"/>
+      <c r="AS21" s="4"/>
+      <c r="AT21" s="4"/>
+      <c r="AU21" s="4"/>
+      <c r="AV21" s="5"/>
+      <c r="AW21" s="1"/>
+      <c r="AX21" s="5"/>
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="4"/>
+      <c r="BA21" s="4"/>
+      <c r="BB21" s="4"/>
+      <c r="BC21" s="4"/>
+      <c r="BD21" s="4"/>
+      <c r="BE21" s="4"/>
+      <c r="BF21" s="4"/>
+      <c r="BG21" s="4"/>
+      <c r="BI21" s="4"/>
+      <c r="BJ21" s="4"/>
+      <c r="BK21" s="4"/>
+      <c r="BL21" s="4"/>
+      <c r="BM21" s="4"/>
+      <c r="BN21" s="4"/>
+      <c r="BO21" s="4"/>
+      <c r="BP21" s="4"/>
+      <c r="BQ21" s="4"/>
+      <c r="BR21" s="4"/>
+      <c r="BT21" s="4"/>
+      <c r="BU21" s="4"/>
+      <c r="BV21" s="4"/>
+      <c r="BW21" s="4"/>
+    </row>
+    <row r="22" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46091.719710648104</v>
+      </c>
+      <c r="C22" s="2">
+        <v>46091.7203240741</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF22" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG22" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="AH22" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="AI22" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="AJ22" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="AK22" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM22" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN22" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="4"/>
+      <c r="AQ22" s="4"/>
+      <c r="AR22" s="4"/>
+      <c r="AS22" s="4"/>
+      <c r="AT22" s="4"/>
+      <c r="AU22" s="4"/>
+      <c r="AV22" s="5"/>
+      <c r="AW22" s="1"/>
+      <c r="AX22" s="5"/>
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="4"/>
+      <c r="BA22" s="4"/>
+      <c r="BB22" s="4"/>
+      <c r="BC22" s="4"/>
+      <c r="BD22" s="4"/>
+      <c r="BE22" s="4"/>
+      <c r="BF22" s="4"/>
+      <c r="BG22" s="4"/>
+      <c r="BI22" s="4"/>
+      <c r="BJ22" s="4"/>
+      <c r="BK22" s="4"/>
+      <c r="BL22" s="4"/>
+      <c r="BM22" s="4"/>
+      <c r="BN22" s="4"/>
+      <c r="BO22" s="4"/>
+      <c r="BP22" s="4"/>
+      <c r="BQ22" s="4"/>
+      <c r="BR22" s="4"/>
+      <c r="BT22" s="4"/>
+      <c r="BU22" s="4"/>
+      <c r="BV22" s="4"/>
+      <c r="BW22" s="4"/>
+    </row>
+    <row r="23" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46091.720439814802</v>
+      </c>
+      <c r="C23" s="2">
+        <v>46091.720949074101</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF23" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG23" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="AH23" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI23" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK23" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN23" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="AO23" s="4"/>
+      <c r="AP23" s="4"/>
+      <c r="AQ23" s="4"/>
+      <c r="AR23" s="4"/>
+      <c r="AS23" s="4"/>
+      <c r="AT23" s="4"/>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="5"/>
+      <c r="AW23" s="1"/>
+      <c r="AX23" s="5"/>
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="4"/>
+      <c r="BA23" s="4"/>
+      <c r="BB23" s="4"/>
+      <c r="BC23" s="4"/>
+      <c r="BD23" s="4"/>
+      <c r="BE23" s="4"/>
+      <c r="BF23" s="4"/>
+      <c r="BG23" s="4"/>
+      <c r="BI23" s="4"/>
+      <c r="BJ23" s="4"/>
+      <c r="BK23" s="4"/>
+      <c r="BL23" s="4"/>
+      <c r="BM23" s="4"/>
+      <c r="BN23" s="4"/>
+      <c r="BO23" s="4"/>
+      <c r="BP23" s="4"/>
+      <c r="BQ23" s="4"/>
+      <c r="BR23" s="4"/>
+      <c r="BT23" s="4"/>
+      <c r="BU23" s="4"/>
+      <c r="BV23" s="4"/>
+      <c r="BW23" s="4"/>
+    </row>
+    <row r="24" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46091.720972222203</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46091.721712963001</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF24" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG24" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="AH24" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AI24" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AJ24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK24" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN24" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="AO24" s="4"/>
+      <c r="AP24" s="4"/>
+      <c r="AQ24" s="4"/>
+      <c r="AR24" s="4"/>
+      <c r="AS24" s="4"/>
+      <c r="AT24" s="4"/>
+      <c r="AU24" s="4"/>
+      <c r="AV24" s="5"/>
+      <c r="AW24" s="1"/>
+      <c r="AX24" s="5"/>
+      <c r="AY24" s="4"/>
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="4"/>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="4"/>
+      <c r="BD24" s="4"/>
+      <c r="BE24" s="4"/>
+      <c r="BF24" s="4"/>
+      <c r="BG24" s="4"/>
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
+      <c r="BK24" s="4"/>
+      <c r="BL24" s="4"/>
+      <c r="BM24" s="4"/>
+      <c r="BN24" s="4"/>
+      <c r="BO24" s="4"/>
+      <c r="BP24" s="4"/>
+      <c r="BQ24" s="4"/>
+      <c r="BR24" s="4"/>
+      <c r="BT24" s="4"/>
+      <c r="BU24" s="4"/>
+      <c r="BV24" s="4"/>
+      <c r="BW24" s="4"/>
+    </row>
+    <row r="25" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46091.721736111103</v>
+      </c>
+      <c r="C25" s="2">
+        <v>46091.722303240698</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="AF25" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG25" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="AH25" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AI25" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="AJ25" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM25" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN25" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO25" s="4"/>
+      <c r="AP25" s="4"/>
+      <c r="AQ25" s="4"/>
+      <c r="AR25" s="4"/>
+      <c r="AS25" s="4"/>
+      <c r="AT25" s="4"/>
+      <c r="AU25" s="4"/>
+      <c r="AV25" s="5"/>
+      <c r="AW25" s="1"/>
+      <c r="AX25" s="5"/>
+      <c r="AY25" s="4"/>
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="4"/>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="4"/>
+      <c r="BD25" s="4"/>
+      <c r="BE25" s="4"/>
+      <c r="BF25" s="4"/>
+      <c r="BG25" s="4"/>
+      <c r="BI25" s="4"/>
+      <c r="BJ25" s="4"/>
+      <c r="BK25" s="4"/>
+      <c r="BL25" s="4"/>
+      <c r="BM25" s="4"/>
+      <c r="BN25" s="4"/>
+      <c r="BO25" s="4"/>
+      <c r="BP25" s="4"/>
+      <c r="BQ25" s="4"/>
+      <c r="BR25" s="4"/>
+      <c r="BT25" s="4"/>
+      <c r="BU25" s="4"/>
+      <c r="BV25" s="4"/>
+      <c r="BW25" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="S2" r:id="rId1" display="https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Lista%20de%20presen%C3%A7a_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Mapa_Participantes_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_OnePager_Beatriz%20de%20Jesus%20Gon.pdf" xr:uid="{E87974D4-56B0-4F0D-BF34-B9D3BCE26344}"/>
+    <hyperlink ref="S6" r:id="rId2" display="https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Oficina1_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Oficina2_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Oficina3_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Oficina4_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Oficina5_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Pergunta/2.Evid%C3%AAncia_Oficina6_Beatriz%20de%20Jesus%20Gon.pdf" xr:uid="{11F358B5-BF25-4F2A-ADF4-0525CCA8839C}"/>
+    <hyperlink ref="AC3" r:id="rId3" xr:uid="{44055C6F-17A0-42F1-9B0A-375C3643D027}"/>
+    <hyperlink ref="BA7" r:id="rId4" display="https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Arquivos%20comprovat%C3%B3rios%202/2.Evid%C3%AAncia_Apresenta%C3%A7%C3%A3o_Beatriz%20de%20Jesus%20Gon.pdf; https://governosp.sharepoint.com/teams/DETRAN-CoordenadoriadeSeguranaViria/Shared%20Documents/Apps/Microsoft%20Forms/Preenchimento%20Ficha%20Pnatrnas/Arquivos%20comprovat%C3%B3rios%202/2.Evid%C3%AAncia_Formul%C3%A1rio_Beatriz%20de%20Jesus%20Gon.pdf" xr:uid="{EBA3005E-AC0C-4150-B845-128DAC590367}"/>
+    <hyperlink ref="AN13" r:id="rId5" xr:uid="{CC2D5311-2A55-42B8-B5A6-667F43A40BA2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E7EE74678CDAA749BF87014A2B4560BF" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f8c5e1a3fd7799846b86452f05f80a69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="31067d2d-e48e-4508-aa64-80d1f142e7dc" xmlns:ns3="ee1a5240-fbb3-422c-a5c8-d7a8e3758d68" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="106dc9b85e5cd8ec46e3be780b487c67" ns2:_="" ns3:_="">
     <xsd:import namespace="31067d2d-e48e-4508-aa64-80d1f142e7dc"/>
@@ -2415,15 +4728,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2436,6 +4740,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43561859-C1AF-40A2-B142-8D8070117294}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE61D396-D4FD-4D0C-BAE6-65E0CB816A7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2454,14 +4766,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43561859-C1AF-40A2-B142-8D8070117294}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B846CAE7-C169-4864-8CF0-F68A797F2E2C}">
   <ds:schemaRefs>
